--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/109.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/109.xlsx
@@ -426,13 +426,13 @@
         <v>-18.97061076731373</v>
       </c>
       <c r="E2">
-        <v>-6.054304644996417</v>
+        <v>-8.617900951582653</v>
       </c>
       <c r="F2">
-        <v>-5.529258831398563</v>
+        <v>-6.331121998283301</v>
       </c>
       <c r="G2">
-        <v>-9.869369717433743</v>
+        <v>-11.67247489812549</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.17530553345604</v>
       </c>
       <c r="E3">
-        <v>-5.678672254534169</v>
+        <v>-11.32994063614032</v>
       </c>
       <c r="F3">
-        <v>-5.663911051299928</v>
+        <v>-5.977763554798057</v>
       </c>
       <c r="G3">
-        <v>-11.3470118556142</v>
+        <v>-10.84107773357508</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.40809464952009</v>
       </c>
       <c r="E4">
-        <v>-6.355593077674741</v>
+        <v>-13.42097709460413</v>
       </c>
       <c r="F4">
-        <v>-5.812192644309566</v>
+        <v>-5.922416200465279</v>
       </c>
       <c r="G4">
-        <v>-9.340966922819591</v>
+        <v>-10.83906161134167</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.78232358372802</v>
       </c>
       <c r="E5">
-        <v>-7.063900754162478</v>
+        <v>-13.03853387923435</v>
       </c>
       <c r="F5">
-        <v>-5.407071960757621</v>
+        <v>-5.78739022596787</v>
       </c>
       <c r="G5">
-        <v>-10.77752188031215</v>
+        <v>-11.00326135954398</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.2899971550383</v>
       </c>
       <c r="E6">
-        <v>-7.775034198430999</v>
+        <v>-11.52526277703916</v>
       </c>
       <c r="F6">
-        <v>-5.459868756713584</v>
+        <v>-5.692362328070798</v>
       </c>
       <c r="G6">
-        <v>-10.5392784705785</v>
+        <v>-11.26992249218673</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.95072006699265</v>
       </c>
       <c r="E7">
-        <v>-8.997835392352188</v>
+        <v>-14.20278190423636</v>
       </c>
       <c r="F7">
-        <v>-5.452342194350457</v>
+        <v>-5.656134263402163</v>
       </c>
       <c r="G7">
-        <v>-11.06996554161475</v>
+        <v>-10.64729495043384</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.74121381031237</v>
       </c>
       <c r="E8">
-        <v>-9.786401213677866</v>
+        <v>-14.60576174923093</v>
       </c>
       <c r="F8">
-        <v>-5.525267892491655</v>
+        <v>-5.66994259527888</v>
       </c>
       <c r="G8">
-        <v>-10.71278747283725</v>
+        <v>-11.04468952642242</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.64542532501602</v>
       </c>
       <c r="E9">
-        <v>-10.73268925621669</v>
+        <v>-15.55952630235642</v>
       </c>
       <c r="F9">
-        <v>-5.314445752881314</v>
+        <v>-5.829507301083066</v>
       </c>
       <c r="G9">
-        <v>-11.6332846600316</v>
+        <v>-11.00836953131107</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.61589542405302</v>
       </c>
       <c r="E10">
-        <v>-12.23597960169898</v>
+        <v>-16.06291147304906</v>
       </c>
       <c r="F10">
-        <v>-5.079789631096567</v>
+        <v>-5.314726860681304</v>
       </c>
       <c r="G10">
-        <v>-9.464741599441862</v>
+        <v>-11.28890184976338</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.59794460841614</v>
       </c>
       <c r="E11">
-        <v>-11.62694060393338</v>
+        <v>-18.17168143572691</v>
       </c>
       <c r="F11">
-        <v>-4.721864967530632</v>
+        <v>-5.515919276472816</v>
       </c>
       <c r="G11">
-        <v>-10.4721670914064</v>
+        <v>-11.65992793053165</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.52995668436338</v>
       </c>
       <c r="E12">
-        <v>-12.97359103349035</v>
+        <v>-17.78628112683011</v>
       </c>
       <c r="F12">
-        <v>-5.026136842093309</v>
+        <v>-5.050460981248543</v>
       </c>
       <c r="G12">
-        <v>-9.945048788461483</v>
+        <v>-10.63423815882696</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.33580082544835</v>
       </c>
       <c r="E13">
-        <v>-14.05602311859578</v>
+        <v>-18.21677597989529</v>
       </c>
       <c r="F13">
-        <v>-5.160772433082562</v>
+        <v>-4.905275533303589</v>
       </c>
       <c r="G13">
-        <v>-9.499820139975979</v>
+        <v>-10.52015675954367</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.96567900716103</v>
       </c>
       <c r="E14">
-        <v>-15.06378519578873</v>
+        <v>-20.08182347148032</v>
       </c>
       <c r="F14">
-        <v>-5.51593194612014</v>
+        <v>-5.15752662780887</v>
       </c>
       <c r="G14">
-        <v>-9.17571442113579</v>
+        <v>-8.530568548624778</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.37453424564086</v>
       </c>
       <c r="E15">
-        <v>-15.78974486395837</v>
+        <v>-19.27774309820436</v>
       </c>
       <c r="F15">
-        <v>-4.960443928867923</v>
+        <v>-5.245148324992388</v>
       </c>
       <c r="G15">
-        <v>-8.348332948324519</v>
+        <v>-9.725827773396484</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.54954189599674</v>
       </c>
       <c r="E16">
-        <v>-16.41184850923609</v>
+        <v>-19.50043080753155</v>
       </c>
       <c r="F16">
-        <v>-5.243648555490466</v>
+        <v>-4.87138264300727</v>
       </c>
       <c r="G16">
-        <v>-7.414606821155236</v>
+        <v>-8.735680018601403</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.51016335611598</v>
       </c>
       <c r="E17">
-        <v>-16.76281430177856</v>
+        <v>-20.78486906117114</v>
       </c>
       <c r="F17">
-        <v>-5.105824172640475</v>
+        <v>-4.995399485833502</v>
       </c>
       <c r="G17">
-        <v>-6.43825079907676</v>
+        <v>-7.576406423841576</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.29973395732865</v>
       </c>
       <c r="E18">
-        <v>-18.4733638456439</v>
+        <v>-23.01057780814906</v>
       </c>
       <c r="F18">
-        <v>-4.867084465152767</v>
+        <v>-4.64804130813538</v>
       </c>
       <c r="G18">
-        <v>-6.018089601414618</v>
+        <v>-6.719676964824664</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.998615722321032</v>
       </c>
       <c r="E19">
-        <v>-18.09690727291225</v>
+        <v>-21.56623913729863</v>
       </c>
       <c r="F19">
-        <v>-4.692625005213873</v>
+        <v>-4.419032681645089</v>
       </c>
       <c r="G19">
-        <v>-5.842249975096229</v>
+        <v>-6.473402171612742</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.689284098982876</v>
       </c>
       <c r="E20">
-        <v>-20.46520408096969</v>
+        <v>-23.98111130052495</v>
       </c>
       <c r="F20">
-        <v>-4.5126439546008</v>
+        <v>-5.043416657336668</v>
       </c>
       <c r="G20">
-        <v>-4.414719564743718</v>
+        <v>-6.144830526840076</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.467258283341204</v>
       </c>
       <c r="E21">
-        <v>-20.47407083307671</v>
+        <v>-24.70276438991329</v>
       </c>
       <c r="F21">
-        <v>-4.666623721494188</v>
+        <v>-4.072792600323267</v>
       </c>
       <c r="G21">
-        <v>-3.514446500248773</v>
+        <v>-5.649165717063776</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.414965612320221</v>
       </c>
       <c r="E22">
-        <v>-20.54140924157076</v>
+        <v>-27.18952607801139</v>
       </c>
       <c r="F22">
-        <v>-3.955304585133434</v>
+        <v>-4.306934017685497</v>
       </c>
       <c r="G22">
-        <v>-4.588893986655854</v>
+        <v>-5.531763840604603</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.598904676078605</v>
       </c>
       <c r="E23">
-        <v>-21.76573200275853</v>
+        <v>-25.92796114658454</v>
       </c>
       <c r="F23">
-        <v>-4.540844213984072</v>
+        <v>-4.01190623455124</v>
       </c>
       <c r="G23">
-        <v>-3.980700423454187</v>
+        <v>-6.018920548344975</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.066794304273832</v>
       </c>
       <c r="E24">
-        <v>-22.34480155954136</v>
+        <v>-25.6096592370594</v>
       </c>
       <c r="F24">
-        <v>-4.1370799745487</v>
+        <v>-3.773405666656763</v>
       </c>
       <c r="G24">
-        <v>-3.050268289096481</v>
+        <v>-4.724265504302192</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.825088385047998</v>
       </c>
       <c r="E25">
-        <v>-22.34420832944636</v>
+        <v>-27.21635728650683</v>
       </c>
       <c r="F25">
-        <v>-4.179802817176553</v>
+        <v>-3.668474855670449</v>
       </c>
       <c r="G25">
-        <v>-2.898675098307714</v>
+        <v>-4.985139803342301</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.860983402275991</v>
       </c>
       <c r="E26">
-        <v>-23.01477570355417</v>
+        <v>-26.71447104071073</v>
       </c>
       <c r="F26">
-        <v>-3.857896377245457</v>
+        <v>-3.212668456147822</v>
       </c>
       <c r="G26">
-        <v>-4.414315678187927</v>
+        <v>-5.63320557701895</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.122858312135047</v>
       </c>
       <c r="E27">
-        <v>-23.64844507144748</v>
+        <v>-27.65852201708978</v>
       </c>
       <c r="F27">
-        <v>-4.23555322466481</v>
+        <v>-3.310820213963097</v>
       </c>
       <c r="G27">
-        <v>-4.060232969489638</v>
+        <v>-5.541016815386866</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.54303511100411</v>
       </c>
       <c r="E28">
-        <v>-23.51887637314002</v>
+        <v>-28.3996475447111</v>
       </c>
       <c r="F28">
-        <v>-3.930449112643569</v>
+        <v>-3.77121540137571</v>
       </c>
       <c r="G28">
-        <v>-3.822300751036679</v>
+        <v>-5.599328764515588</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.041924327018283</v>
       </c>
       <c r="E29">
-        <v>-22.82151401832882</v>
+        <v>-28.39650478374978</v>
       </c>
       <c r="F29">
-        <v>-3.708972591487109</v>
+        <v>-3.338105883180203</v>
       </c>
       <c r="G29">
-        <v>-3.87803047464477</v>
+        <v>-6.743721457076392</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.536436861509591</v>
       </c>
       <c r="E30">
-        <v>-21.8749361534535</v>
+        <v>-26.84606396689963</v>
       </c>
       <c r="F30">
-        <v>-3.874427099590815</v>
+        <v>-3.774488129649966</v>
       </c>
       <c r="G30">
-        <v>-4.607413178402537</v>
+        <v>-6.046133232677785</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.957858514820684</v>
       </c>
       <c r="E31">
-        <v>-23.35052129495686</v>
+        <v>-27.25567802631544</v>
       </c>
       <c r="F31">
-        <v>-3.946210153914023</v>
+        <v>-3.589955508235919</v>
       </c>
       <c r="G31">
-        <v>-4.994429194125496</v>
+        <v>-6.403705256374465</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.247570768281803</v>
       </c>
       <c r="E32">
-        <v>-22.26661745579893</v>
+        <v>-28.04716471337606</v>
       </c>
       <c r="F32">
-        <v>-3.378343099373773</v>
+        <v>-3.372407369602706</v>
       </c>
       <c r="G32">
-        <v>-5.573334360941231</v>
+        <v>-6.899896442891509</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.371629316487701</v>
       </c>
       <c r="E33">
-        <v>-22.54822061196591</v>
+        <v>-24.20632589834842</v>
       </c>
       <c r="F33">
-        <v>-3.79378400252368</v>
+        <v>-3.519596205530691</v>
       </c>
       <c r="G33">
-        <v>-5.983318941615653</v>
+        <v>-6.367388571808661</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.315184791606108</v>
       </c>
       <c r="E34">
-        <v>-20.91351847925505</v>
+        <v>-27.67094362129281</v>
       </c>
       <c r="F34">
-        <v>-3.760702761509023</v>
+        <v>-3.983628373578111</v>
       </c>
       <c r="G34">
-        <v>-4.26081561316854</v>
+        <v>-7.878453977753601</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.086014749695518</v>
       </c>
       <c r="E35">
-        <v>-21.23504466227365</v>
+        <v>-25.55838785434456</v>
       </c>
       <c r="F35">
-        <v>-3.53035115240244</v>
+        <v>-3.641855134790785</v>
       </c>
       <c r="G35">
-        <v>-5.430080434365888</v>
+        <v>-5.996432012496706</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.710454108785413</v>
       </c>
       <c r="E36">
-        <v>-20.98698391308148</v>
+        <v>-24.48576444393974</v>
       </c>
       <c r="F36">
-        <v>-3.565969490293631</v>
+        <v>-3.596276870397396</v>
       </c>
       <c r="G36">
-        <v>-5.732995351209201</v>
+        <v>-7.593237237363232</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.225544604438714</v>
       </c>
       <c r="E37">
-        <v>-19.636488809092</v>
+        <v>-26.07982352243177</v>
       </c>
       <c r="F37">
-        <v>-3.35609519867368</v>
+        <v>-3.923620172736195</v>
       </c>
       <c r="G37">
-        <v>-5.359320834009505</v>
+        <v>-5.523616588032456</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.679373246585907</v>
       </c>
       <c r="E38">
-        <v>-19.58479174982044</v>
+        <v>-25.13230826343686</v>
       </c>
       <c r="F38">
-        <v>-3.797500168454259</v>
+        <v>-3.774305211616733</v>
       </c>
       <c r="G38">
-        <v>-5.937348706257334</v>
+        <v>-5.711682059027374</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.118943837801852</v>
       </c>
       <c r="E39">
-        <v>-20.20605762740674</v>
+        <v>-25.37477634722955</v>
       </c>
       <c r="F39">
-        <v>-3.653151709085615</v>
+        <v>-3.938506216488368</v>
       </c>
       <c r="G39">
-        <v>-6.312645390771272</v>
+        <v>-6.399537279540523</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.590690848744272</v>
       </c>
       <c r="E40">
-        <v>-19.80219472998068</v>
+        <v>-22.46957913234871</v>
       </c>
       <c r="F40">
-        <v>-3.410062353301152</v>
+        <v>-3.497920814519029</v>
       </c>
       <c r="G40">
-        <v>-6.407379961923056</v>
+        <v>-6.671531701047043</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.133416810669167</v>
       </c>
       <c r="E41">
-        <v>-19.6014746480647</v>
+        <v>-22.40148446869537</v>
       </c>
       <c r="F41">
-        <v>-3.837592475556566</v>
+        <v>-3.973313696950854</v>
       </c>
       <c r="G41">
-        <v>-6.624773555850378</v>
+        <v>-6.138262404490162</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.775142358653185</v>
       </c>
       <c r="E42">
-        <v>-18.10460115025128</v>
+        <v>-22.88850373432429</v>
       </c>
       <c r="F42">
-        <v>-4.126038376906257</v>
+        <v>-4.011174562418307</v>
       </c>
       <c r="G42">
-        <v>-5.275441541680991</v>
+        <v>-6.016497229010229</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.535306235470422</v>
       </c>
       <c r="E43">
-        <v>-17.24859276552937</v>
+        <v>-22.68571866826081</v>
       </c>
       <c r="F43">
-        <v>-3.571562347734005</v>
+        <v>-4.33365113647896</v>
       </c>
       <c r="G43">
-        <v>-6.08812750284344</v>
+        <v>-6.918001816445783</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.417512157391875</v>
       </c>
       <c r="E44">
-        <v>-16.05155406023782</v>
+        <v>-22.26157273575439</v>
       </c>
       <c r="F44">
-        <v>-3.780274991064982</v>
+        <v>-3.88566586861973</v>
       </c>
       <c r="G44">
-        <v>-5.787467067512369</v>
+        <v>-6.391803845160785</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.418341431189887</v>
       </c>
       <c r="E45">
-        <v>-17.15648360421336</v>
+        <v>-21.34396351910614</v>
       </c>
       <c r="F45">
-        <v>-3.691520152298966</v>
+        <v>-4.203196529106466</v>
       </c>
       <c r="G45">
-        <v>-4.920395464230775</v>
+        <v>-5.943731438057048</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.522449238171977</v>
       </c>
       <c r="E46">
-        <v>-15.74886180061712</v>
+        <v>-20.5829353482211</v>
       </c>
       <c r="F46">
-        <v>-3.434385700603429</v>
+        <v>-4.217214702016979</v>
       </c>
       <c r="G46">
-        <v>-6.507672939035277</v>
+        <v>-6.396673657649053</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.711440399047363</v>
       </c>
       <c r="E47">
-        <v>-15.4295681552843</v>
+        <v>-19.94673909183151</v>
       </c>
       <c r="F47">
-        <v>-3.639887380190852</v>
+        <v>-4.378213453527596</v>
       </c>
       <c r="G47">
-        <v>-6.455379561696949</v>
+        <v>-5.656723692529932</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.96302776032615</v>
       </c>
       <c r="E48">
-        <v>-15.13092435142645</v>
+        <v>-20.05165024916721</v>
       </c>
       <c r="F48">
-        <v>-3.714930493140992</v>
+        <v>-4.068948946066495</v>
       </c>
       <c r="G48">
-        <v>-6.582434988948639</v>
+        <v>-6.540354644598962</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.253764360875204</v>
       </c>
       <c r="E49">
-        <v>-13.30733503938164</v>
+        <v>-19.35253084644103</v>
       </c>
       <c r="F49">
-        <v>-3.229572141236265</v>
+        <v>-4.172767995500171</v>
       </c>
       <c r="G49">
-        <v>-5.584153223763569</v>
+        <v>-6.070008887107009</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.564791088538144</v>
       </c>
       <c r="E50">
-        <v>-14.58825919719128</v>
+        <v>-18.7271123581897</v>
       </c>
       <c r="F50">
-        <v>-3.748833677525762</v>
+        <v>-3.37392376801674</v>
       </c>
       <c r="G50">
-        <v>-6.391406579696073</v>
+        <v>-6.35794689593066</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.878848650970759</v>
       </c>
       <c r="E51">
-        <v>-14.09870851459208</v>
+        <v>-18.58237327195654</v>
       </c>
       <c r="F51">
-        <v>-3.413899672734262</v>
+        <v>-4.163903201638498</v>
       </c>
       <c r="G51">
-        <v>-6.599676310117163</v>
+        <v>-5.949501718931998</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.188990593326266</v>
       </c>
       <c r="E52">
-        <v>-12.19132884798335</v>
+        <v>-18.84314997616224</v>
       </c>
       <c r="F52">
-        <v>-3.994647799337738</v>
+        <v>-4.310815680884239</v>
       </c>
       <c r="G52">
-        <v>-5.982911744514323</v>
+        <v>-6.359390293785782</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.488004303926705</v>
       </c>
       <c r="E53">
-        <v>-11.37599068832432</v>
+        <v>-17.23502545740239</v>
       </c>
       <c r="F53">
-        <v>-3.403692688109255</v>
+        <v>-4.200548572815852</v>
       </c>
       <c r="G53">
-        <v>-5.382348988780676</v>
+        <v>-5.794250375322337</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.776567699097797</v>
       </c>
       <c r="E54">
-        <v>-11.6183319748448</v>
+        <v>-16.6896296333406</v>
       </c>
       <c r="F54">
-        <v>-3.50247317717296</v>
+        <v>-3.922570175714258</v>
       </c>
       <c r="G54">
-        <v>-7.081208400986314</v>
+        <v>-6.170199237307512</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.053893370984444</v>
       </c>
       <c r="E55">
-        <v>-11.88545759960926</v>
+        <v>-17.58965931389107</v>
       </c>
       <c r="F55">
-        <v>-3.280138287410331</v>
+        <v>-4.140499987473092</v>
       </c>
       <c r="G55">
-        <v>-5.270664424467824</v>
+        <v>-5.646729155546873</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.320249460483748</v>
       </c>
       <c r="E56">
-        <v>-9.716101183182792</v>
+        <v>-14.3706524357007</v>
       </c>
       <c r="F56">
-        <v>-3.541616844431918</v>
+        <v>-4.630819298157934</v>
       </c>
       <c r="G56">
-        <v>-5.642653873988031</v>
+        <v>-5.17637677696384</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.577430657980963</v>
       </c>
       <c r="E57">
-        <v>-10.53205521530686</v>
+        <v>-15.56821191550313</v>
       </c>
       <c r="F57">
-        <v>-3.635889314607325</v>
+        <v>-4.169823886203369</v>
       </c>
       <c r="G57">
-        <v>-6.557506581037926</v>
+        <v>-6.047775263265263</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.82199966231375</v>
       </c>
       <c r="E58">
-        <v>-9.82311355245805</v>
+        <v>-13.50863929444461</v>
       </c>
       <c r="F58">
-        <v>-3.927184302898891</v>
+        <v>-4.475612159180079</v>
       </c>
       <c r="G58">
-        <v>-6.254475795100738</v>
+        <v>-6.682436638053403</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.056114060295366</v>
       </c>
       <c r="E59">
-        <v>-9.772362944254088</v>
+        <v>-16.64913601876401</v>
       </c>
       <c r="F59">
-        <v>-3.759849144020601</v>
+        <v>-4.565973667597308</v>
       </c>
       <c r="G59">
-        <v>-6.446758901112688</v>
+        <v>-6.893619648549051</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.276192041953241</v>
       </c>
       <c r="E60">
-        <v>-9.603093114321377</v>
+        <v>-15.32302674730584</v>
       </c>
       <c r="F60">
-        <v>-3.857331786086603</v>
+        <v>-4.577226689979462</v>
       </c>
       <c r="G60">
-        <v>-7.243819087329776</v>
+        <v>-5.845169876261867</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.479326158837312</v>
       </c>
       <c r="E61">
-        <v>-8.633216250676593</v>
+        <v>-14.62536551321013</v>
       </c>
       <c r="F61">
-        <v>-4.292350461763172</v>
+        <v>-4.684462584925699</v>
       </c>
       <c r="G61">
-        <v>-6.899270749784587</v>
+        <v>-6.715657962539989</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.661271790445138</v>
       </c>
       <c r="E62">
-        <v>-7.813277161425776</v>
+        <v>-13.96967417621752</v>
       </c>
       <c r="F62">
-        <v>-3.91903455225804</v>
+        <v>-4.460628717514107</v>
       </c>
       <c r="G62">
-        <v>-6.598630177726753</v>
+        <v>-7.427157099294614</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.812810884384668</v>
       </c>
       <c r="E63">
-        <v>-8.329025066159353</v>
+        <v>-13.41478667063565</v>
       </c>
       <c r="F63">
-        <v>-4.049285653420399</v>
+        <v>-4.665627570473377</v>
       </c>
       <c r="G63">
-        <v>-6.481685156551999</v>
+        <v>-7.607022348988757</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.925547034721502</v>
       </c>
       <c r="E64">
-        <v>-6.85190024349339</v>
+        <v>-12.35753290101287</v>
       </c>
       <c r="F64">
-        <v>-3.968858732210722</v>
+        <v>-4.667031525767414</v>
       </c>
       <c r="G64">
-        <v>-7.248880911459321</v>
+        <v>-7.601017019380518</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.9876844824057</v>
       </c>
       <c r="E65">
-        <v>-6.832821782499074</v>
+        <v>-13.15084909157259</v>
       </c>
       <c r="F65">
-        <v>-3.962116896128697</v>
+        <v>-5.182367846945495</v>
       </c>
       <c r="G65">
-        <v>-7.552742644326866</v>
+        <v>-8.163104614856756</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.988296714716023</v>
       </c>
       <c r="E66">
-        <v>-6.837001564008154</v>
+        <v>-13.08277707028929</v>
       </c>
       <c r="F66">
-        <v>-4.296123641106707</v>
+        <v>-5.095606893927018</v>
       </c>
       <c r="G66">
-        <v>-7.743373788114719</v>
+        <v>-7.75095493739965</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.920480779246494</v>
       </c>
       <c r="E67">
-        <v>-7.135486871275731</v>
+        <v>-12.27994655583945</v>
       </c>
       <c r="F67">
-        <v>-4.469602787083944</v>
+        <v>-5.089345712590328</v>
       </c>
       <c r="G67">
-        <v>-8.867234477240963</v>
+        <v>-8.175264248622499</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.776055566069202</v>
       </c>
       <c r="E68">
-        <v>-7.519890915890836</v>
+        <v>-13.20508209628845</v>
       </c>
       <c r="F68">
-        <v>-4.258812321591911</v>
+        <v>-5.306681634630873</v>
       </c>
       <c r="G68">
-        <v>-8.602874173748001</v>
+        <v>-8.54587320065283</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.552620144415369</v>
       </c>
       <c r="E69">
-        <v>-7.867469409875567</v>
+        <v>-12.63038251692302</v>
       </c>
       <c r="F69">
-        <v>-3.831428692133676</v>
+        <v>-5.268088305177528</v>
       </c>
       <c r="G69">
-        <v>-7.741609267342287</v>
+        <v>-8.563323086190328</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.250978648635717</v>
       </c>
       <c r="E70">
-        <v>-6.558527583380473</v>
+        <v>-11.54199096002349</v>
       </c>
       <c r="F70">
-        <v>-4.440811013541255</v>
+        <v>-5.307861495537875</v>
       </c>
       <c r="G70">
-        <v>-8.443908398043277</v>
+        <v>-7.929211261961707</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.874480949321846</v>
       </c>
       <c r="E71">
-        <v>-7.881992226018166</v>
+        <v>-11.63301781605168</v>
       </c>
       <c r="F71">
-        <v>-4.872511825324978</v>
+        <v>-4.987191929926738</v>
       </c>
       <c r="G71">
-        <v>-8.506772347288498</v>
+        <v>-8.786377712989802</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.434585524093645</v>
       </c>
       <c r="E72">
-        <v>-7.415672615078311</v>
+        <v>-13.93815146865013</v>
       </c>
       <c r="F72">
-        <v>-4.794135803275796</v>
+        <v>-5.612819114761937</v>
       </c>
       <c r="G72">
-        <v>-8.611342549237456</v>
+        <v>-8.782318984158657</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.93924953712291</v>
       </c>
       <c r="E73">
-        <v>-7.732439371914852</v>
+        <v>-13.10848974570484</v>
       </c>
       <c r="F73">
-        <v>-4.94345709921892</v>
+        <v>-5.004189845517149</v>
       </c>
       <c r="G73">
-        <v>-7.857408839760454</v>
+        <v>-9.087432103240046</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.405928894684699</v>
       </c>
       <c r="E74">
-        <v>-7.170066298798301</v>
+        <v>-13.49778001377422</v>
       </c>
       <c r="F74">
-        <v>-5.005225589185846</v>
+        <v>-5.027613647859456</v>
       </c>
       <c r="G74">
-        <v>-8.036780818169246</v>
+        <v>-8.042160454670562</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.850760367216335</v>
       </c>
       <c r="E75">
-        <v>-7.47093811186792</v>
+        <v>-14.26785607572658</v>
       </c>
       <c r="F75">
-        <v>-4.475041233197564</v>
+        <v>-5.380474411760773</v>
       </c>
       <c r="G75">
-        <v>-8.767103716860166</v>
+        <v>-7.541069660755396</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.290661555133973</v>
       </c>
       <c r="E76">
-        <v>-7.532801595286704</v>
+        <v>-14.1524479156411</v>
       </c>
       <c r="F76">
-        <v>-4.91231114683293</v>
+        <v>-5.715729908853107</v>
       </c>
       <c r="G76">
-        <v>-8.735252958226837</v>
+        <v>-8.036843718534492</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.745972187798876</v>
       </c>
       <c r="E77">
-        <v>-7.910820491550996</v>
+        <v>-14.09536197230041</v>
       </c>
       <c r="F77">
-        <v>-5.28980883180778</v>
+        <v>-5.581034137039067</v>
       </c>
       <c r="G77">
-        <v>-8.116816567126666</v>
+        <v>-8.521097077836924</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.228108301564024</v>
       </c>
       <c r="E78">
-        <v>-9.823430545638587</v>
+        <v>-14.20404082001049</v>
       </c>
       <c r="F78">
-        <v>-5.077353099545663</v>
+        <v>-5.96329877681939</v>
       </c>
       <c r="G78">
-        <v>-7.427193515295546</v>
+        <v>-7.142403835279742</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.754702270740588</v>
       </c>
       <c r="E79">
-        <v>-10.56294393651318</v>
+        <v>-15.98145781107309</v>
       </c>
       <c r="F79">
-        <v>-5.230815786457661</v>
+        <v>-5.625207654285462</v>
       </c>
       <c r="G79">
-        <v>-8.368828535758146</v>
+        <v>-7.916886100919</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.334192818854796</v>
       </c>
       <c r="E80">
-        <v>-10.23132831340549</v>
+        <v>-16.46148964130817</v>
       </c>
       <c r="F80">
-        <v>-5.153156391335214</v>
+        <v>-5.941316938713091</v>
       </c>
       <c r="G80">
-        <v>-8.1976965051966</v>
+        <v>-7.546734004173089</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.976255794702156</v>
       </c>
       <c r="E81">
-        <v>-11.13996209457054</v>
+        <v>-16.17788037115579</v>
       </c>
       <c r="F81">
-        <v>-5.134420358502608</v>
+        <v>-5.849601361738162</v>
       </c>
       <c r="G81">
-        <v>-7.580657164314001</v>
+        <v>-7.357271482960599</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.686420218564476</v>
       </c>
       <c r="E82">
-        <v>-11.71510546438872</v>
+        <v>-16.05527646587213</v>
       </c>
       <c r="F82">
-        <v>-5.261950652902242</v>
+        <v>-6.177257050068781</v>
       </c>
       <c r="G82">
-        <v>-6.640379467522502</v>
+        <v>-6.996435261362197</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.464988833679212</v>
       </c>
       <c r="E83">
-        <v>-14.02113122636668</v>
+        <v>-18.32633788003686</v>
       </c>
       <c r="F83">
-        <v>-5.313559669421625</v>
+        <v>-6.105327502948395</v>
       </c>
       <c r="G83">
-        <v>-7.863775018832473</v>
+        <v>-7.422674620634441</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.313116607630239</v>
       </c>
       <c r="E84">
-        <v>-14.09391738909196</v>
+        <v>-17.96703063837227</v>
       </c>
       <c r="F84">
-        <v>-5.55167222936682</v>
+        <v>-6.031238176885827</v>
       </c>
       <c r="G84">
-        <v>-6.604228310233661</v>
+        <v>-7.408568386091606</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.227103259810989</v>
       </c>
       <c r="E85">
-        <v>-13.88766804041262</v>
+        <v>-18.17118783206007</v>
       </c>
       <c r="F85">
-        <v>-5.587005500193231</v>
+        <v>-5.830378339336558</v>
       </c>
       <c r="G85">
-        <v>-7.647470594387572</v>
+        <v>-6.567428286019122</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.208162636312178</v>
       </c>
       <c r="E86">
-        <v>-14.875020285253</v>
+        <v>-19.93333480876881</v>
       </c>
       <c r="F86">
-        <v>-5.330258264594019</v>
+        <v>-5.931383143358497</v>
       </c>
       <c r="G86">
-        <v>-7.282386942862285</v>
+        <v>-7.347975471086325</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.255604931516171</v>
       </c>
       <c r="E87">
-        <v>-17.40308618477506</v>
+        <v>-22.10966054669308</v>
       </c>
       <c r="F87">
-        <v>-5.746807761884734</v>
+        <v>-6.075842462141222</v>
       </c>
       <c r="G87">
-        <v>-7.096880523569224</v>
+        <v>-6.471842904663745</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.374920015991029</v>
       </c>
       <c r="E88">
-        <v>-19.82018182873914</v>
+        <v>-23.88645713681663</v>
       </c>
       <c r="F88">
-        <v>-5.916038616743804</v>
+        <v>-6.040227291661862</v>
       </c>
       <c r="G88">
-        <v>-7.871296578297697</v>
+        <v>-7.621201415533455</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.568804610582546</v>
       </c>
       <c r="E89">
-        <v>-19.73951612124051</v>
+        <v>-24.23964188162286</v>
       </c>
       <c r="F89">
-        <v>-5.962158508560274</v>
+        <v>-6.404048884203935</v>
       </c>
       <c r="G89">
-        <v>-7.090140252851268</v>
+        <v>-7.455664206933278</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.844951825335639</v>
       </c>
       <c r="E90">
-        <v>-21.35688778392403</v>
+        <v>-25.07608273015762</v>
       </c>
       <c r="F90">
-        <v>-5.909977774205418</v>
+        <v>-6.078001845156924</v>
       </c>
       <c r="G90">
-        <v>-7.589496320903855</v>
+        <v>-7.308815027902287</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.20871807152434</v>
       </c>
       <c r="E91">
-        <v>-23.68513929633163</v>
+        <v>-28.02972555997252</v>
       </c>
       <c r="F91">
-        <v>-5.348078915407502</v>
+        <v>-5.855538675215144</v>
       </c>
       <c r="G91">
-        <v>-7.882737823681418</v>
+        <v>-6.901174313469668</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.664309448789516</v>
       </c>
       <c r="E92">
-        <v>-25.35356950345163</v>
+        <v>-31.73690420042676</v>
       </c>
       <c r="F92">
-        <v>-5.78757076844223</v>
+        <v>-6.740573721587494</v>
       </c>
       <c r="G92">
-        <v>-7.626332761119325</v>
+        <v>-7.002000288413711</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.216950764636251</v>
       </c>
       <c r="E93">
-        <v>-26.96781651906985</v>
+        <v>-31.83668459671177</v>
       </c>
       <c r="F93">
-        <v>-5.773605649679884</v>
+        <v>-6.419004611016388</v>
       </c>
       <c r="G93">
-        <v>-7.513694759691163</v>
+        <v>-7.772516520496923</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.859309608521209</v>
       </c>
       <c r="E94">
-        <v>-29.1512112049201</v>
+        <v>-33.30627177439197</v>
       </c>
       <c r="F94">
-        <v>-5.389423142035964</v>
+        <v>-5.655716956893445</v>
       </c>
       <c r="G94">
-        <v>-8.482923177223588</v>
+        <v>-7.318356020146466</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.588303025633206</v>
       </c>
       <c r="E95">
-        <v>-31.54902687079653</v>
+        <v>-35.55784037219069</v>
       </c>
       <c r="F95">
-        <v>-5.666479030441814</v>
+        <v>-5.829535015936586</v>
       </c>
       <c r="G95">
-        <v>-8.087094489275088</v>
+        <v>-8.071574651786985</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.391356120424764</v>
       </c>
       <c r="E96">
-        <v>-33.79705646615826</v>
+        <v>-39.10692998503716</v>
       </c>
       <c r="F96">
-        <v>-4.939424983958211</v>
+        <v>-5.3177010603905</v>
       </c>
       <c r="G96">
-        <v>-8.943317434824493</v>
+        <v>-8.161558590089916</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.242762271548651</v>
       </c>
       <c r="E97">
-        <v>-35.95390750161255</v>
+        <v>-40.59627942328683</v>
       </c>
       <c r="F97">
-        <v>-5.229817259877977</v>
+        <v>-5.89677758540023</v>
       </c>
       <c r="G97">
-        <v>-8.120077454482848</v>
+        <v>-9.155225454793241</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.13561444685685</v>
       </c>
       <c r="E98">
-        <v>-38.47013823431556</v>
+        <v>-40.27407849764109</v>
       </c>
       <c r="F98">
-        <v>-4.926625472749629</v>
+        <v>-5.643993573854405</v>
       </c>
       <c r="G98">
-        <v>-8.903772968357899</v>
+        <v>-8.86120266326841</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.014702899394871</v>
       </c>
       <c r="E99">
-        <v>-39.46249897140842</v>
+        <v>-43.91707507598461</v>
       </c>
       <c r="F99">
-        <v>-4.61066901594284</v>
+        <v>-4.858051798464059</v>
       </c>
       <c r="G99">
-        <v>-9.243054227950106</v>
+        <v>-9.320418366657334</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.896822140458404</v>
       </c>
       <c r="E100">
-        <v>-42.97243992645858</v>
+        <v>-46.2093003134242</v>
       </c>
       <c r="F100">
-        <v>-4.908039100126032</v>
+        <v>-4.882974578455329</v>
       </c>
       <c r="G100">
-        <v>-9.762227221600771</v>
+        <v>-8.266612131687609</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.684134192870516</v>
       </c>
       <c r="E101">
-        <v>-45.00826975829489</v>
+        <v>-48.81124034155188</v>
       </c>
       <c r="F101">
-        <v>-4.962695958679678</v>
+        <v>-4.840349925594234</v>
       </c>
       <c r="G101">
-        <v>-8.734170409835496</v>
+        <v>-9.15191490925397</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.46346372000732</v>
       </c>
       <c r="E102">
-        <v>-47.64910145331894</v>
+        <v>-51.34398755107937</v>
       </c>
       <c r="F102">
-        <v>-3.9187843267234</v>
+        <v>-4.725593011255576</v>
       </c>
       <c r="G102">
-        <v>-10.49789665133761</v>
+        <v>-9.081330767811169</v>
       </c>
     </row>
   </sheetData>
